--- a/data/reservation-data.xlsx
+++ b/data/reservation-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\2026_KDMHS\공업일반\webprojec\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A3648D-081B-444E-8B9C-1C1C53E06B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D078A00-95A8-4E08-A6E9-41DA9D6E660A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6420" yWindow="2076" windowWidth="17184" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="206">
   <si>
     <t>title</t>
   </si>
@@ -64,18 +64,9 @@
     <t>넥스트 투 노멀</t>
   </si>
   <si>
-    <t>../img/po-mam.gif</t>
-  </si>
-  <si>
     <t>../img/po-stra.gif</t>
   </si>
   <si>
-    <t>../img/po-nak.jpg</t>
-  </si>
-  <si>
-    <t>../img/po-red.gif</t>
-  </si>
-  <si>
     <t>../img/po-long.gif</t>
   </si>
   <si>
@@ -94,69 +85,27 @@
     <t>../img/po-next.gif</t>
   </si>
   <si>
-    <t>행복해지는 주문 맘마미아!</t>
-  </si>
-  <si>
     <t>흐린 가을 하늘에 편지를 써</t>
   </si>
   <si>
     <t>문제는 너의 음악</t>
   </si>
   <si>
-    <t>나의 겨울은 널 위한 봄</t>
-  </si>
-  <si>
-    <t>당신이 주는 아픔은 왜 이리 달콤할까요</t>
-  </si>
-  <si>
-    <t>2025.07.26 - 2025.10.25</t>
-  </si>
-  <si>
     <t>2025.07.28 - 2025.10.12</t>
   </si>
   <si>
-    <t>2025.07.15 - 2025.10.12</t>
-  </si>
-  <si>
     <t>광림아트센터 BBCH홀</t>
   </si>
   <si>
-    <t>LG아트센터 서울 LG SIGNATURE 홀</t>
-  </si>
-  <si>
     <t>대학로 TOM 2관</t>
   </si>
   <si>
-    <t>링크아트센터드림 드림3관</t>
-  </si>
-  <si>
-    <t>대학로 자유극장</t>
-  </si>
-  <si>
-    <t>링크아트센터드림 드림4관</t>
-  </si>
-  <si>
-    <t>링크아트센터드림 드림2관</t>
-  </si>
-  <si>
     <t>박은태·최재림·조정은·차지연 외</t>
   </si>
   <si>
-    <t>최정원·신영숙·루나·최태이·홍지민 외</t>
-  </si>
-  <si>
     <t>임준혁·서영택 외</t>
   </si>
   <si>
-    <t>박새힘·이아진 외</t>
-  </si>
-  <si>
-    <t>박민성·문태유 외</t>
-  </si>
-  <si>
-    <t>강정우·조성윤 외</t>
-  </si>
-  <si>
     <t>type</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -267,10 +216,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>헤이그</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>피리 부는 사나이</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -761,14 +706,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>2026.04.22 - 2026.07.20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>임찬민·김이후 외</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>../img/po-black.gif</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -786,6 +723,74 @@
   </si>
   <si>
     <t>https://tickets.interpark.com/goods/26006404#</t>
+  </si>
+  <si>
+    <t>../img/po-pen.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>함께라면 쓸 수 있어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.04.09 - 2026.06.29</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SH아트홀</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장보람·문진아 외</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://m.ticketlink.co.kr/product/61930</t>
+  </si>
+  <si>
+    <t>임준혁·선한국 외</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://m.ticketlink.co.kr/product/63166</t>
+  </si>
+  <si>
+    <t>링크아트센터 페이코홀</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김려원·정민 외</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>링크더스페이스 1관</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김이후·기세중 외</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://m.ticketlink.co.kr/product/63148</t>
+  </si>
+  <si>
+    <t>https://www.ticketlink.co.kr/product/63096</t>
+  </si>
+  <si>
+    <t>동덕여자대학교 공연예술센터 코튼홀</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.06.23 - 2026.09.20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>빗속의 살인</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>../img/po-jong.gif</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1173,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="38.296875" bestFit="1" customWidth="1"/>
@@ -1186,7 +1191,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1215,25 +1220,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -1241,25 +1246,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -1267,25 +1272,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -1293,25 +1298,25 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -1319,49 +1324,51 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>191</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -1369,25 +1376,25 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -1395,25 +1402,25 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="G9" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1421,25 +1428,25 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -1447,25 +1454,25 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G11" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -1473,25 +1480,25 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -1499,25 +1506,25 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F13" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="G13" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -1525,25 +1532,25 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F14" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G14" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -1551,25 +1558,25 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="F15" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G15" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -1577,25 +1584,25 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="F16" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G16" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -1603,25 +1610,25 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F17" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G17" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -1629,25 +1636,25 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F18" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G18" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -1655,22 +1662,22 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="H19" s="2"/>
     </row>
@@ -1679,25 +1686,25 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="G20" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -1705,34 +1712,36 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="G21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D22" t="s">
         <v>158</v>
@@ -1755,25 +1764,25 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D23" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E23" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F23" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="G23" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -1781,25 +1790,25 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
+        <v>177</v>
+      </c>
+      <c r="D24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E24" t="s">
         <v>181</v>
       </c>
-      <c r="D24" t="s">
-        <v>182</v>
-      </c>
-      <c r="E24" t="s">
-        <v>183</v>
-      </c>
       <c r="F24" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -1807,85 +1816,79 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D25" t="s">
+        <v>180</v>
+      </c>
+      <c r="E25" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" t="s">
+        <v>198</v>
+      </c>
+      <c r="G25" t="s">
         <v>197</v>
       </c>
-      <c r="E25" t="s">
-        <v>199</v>
-      </c>
-      <c r="F25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F26" t="s">
+        <v>202</v>
+      </c>
+      <c r="G26" t="s">
+        <v>199</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F26" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" t="s">
-        <v>202</v>
-      </c>
-      <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" t="s">
-        <v>201</v>
-      </c>
-      <c r="F27" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="2"/>
+        <v>170</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -1893,13 +1896,13 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
@@ -1907,13 +1910,13 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -1921,13 +1924,25 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>191</v>
+        <v>164</v>
+      </c>
+      <c r="E31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
@@ -1935,25 +1950,13 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>182</v>
-      </c>
-      <c r="E32" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G32" t="s">
-        <v>185</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
@@ -1961,53 +1964,39 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>183</v>
       </c>
       <c r="D34" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A35">
-        <v>1</v>
-      </c>
-      <c r="B35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" t="s">
-        <v>203</v>
-      </c>
-      <c r="D35" t="s">
-        <v>194</v>
-      </c>
-      <c r="E35" t="s">
-        <v>204</v>
-      </c>
-      <c r="F35" t="s">
-        <v>205</v>
-      </c>
-      <c r="G35" t="s">
-        <v>206</v>
-      </c>
-      <c r="H35" t="s">
-        <v>207</v>
+        <v>176</v>
+      </c>
+      <c r="E34" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" t="s">
+        <v>185</v>
+      </c>
+      <c r="G34" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/data/reservation-data.xlsx
+++ b/data/reservation-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\2026_KDMHS\공업일반\webprojec\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D078A00-95A8-4E08-A6E9-41DA9D6E660A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1665BA2A-96DA-4557-A74C-2FB5EA194D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="2076" windowWidth="17184" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5856" yWindow="2076" windowWidth="17184" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="199">
   <si>
     <t>title</t>
   </si>
@@ -172,10 +172,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>렘피카</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>슬립노모어 서울</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -345,29 +341,6 @@
   </si>
   <si>
     <t>2026.06.04 - 2026.08.30</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>../img/po-lem.gif</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>여자는 라파엘라</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://tickets.interpark.com/goods/26000685#</t>
-  </si>
-  <si>
-    <t>코엑스아티움 우리은행홀</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.03.21 - 2026.06.20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>김선영·박혜나·정선아·차지연·린아 외</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1178,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="38.296875" bestFit="1" customWidth="1"/>
@@ -1229,7 +1202,7 @@
         <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
         <v>32</v>
@@ -1272,25 +1245,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
         <v>65</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>66</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>67</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>68</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>69</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -1301,13 +1274,13 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
         <v>73</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>74</v>
-      </c>
-      <c r="E5" t="s">
-        <v>75</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
@@ -1316,7 +1289,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -1324,25 +1297,25 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -1353,22 +1326,22 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -1379,22 +1352,22 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" t="s">
         <v>82</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -1405,22 +1378,22 @@
         <v>45</v>
       </c>
       <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s">
         <v>90</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" t="s">
-        <v>93</v>
-      </c>
-      <c r="G9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1431,22 +1404,22 @@
         <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -1457,22 +1430,22 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="G11" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -1483,22 +1456,22 @@
         <v>48</v>
       </c>
       <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" t="s">
         <v>103</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>104</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>105</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>107</v>
       </c>
-      <c r="G12" t="s">
-        <v>102</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -1509,22 +1482,22 @@
         <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -1535,22 +1508,22 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="F14" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -1561,22 +1534,22 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F15" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="G15" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -1587,22 +1560,22 @@
         <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F16" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="G16" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -1613,22 +1586,22 @@
         <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="F17" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -1636,50 +1609,50 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>153</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>154</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
@@ -1689,22 +1662,22 @@
         <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="F20" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="G20" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -1715,22 +1688,22 @@
         <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F21" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="G21" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -1744,19 +1717,19 @@
         <v>156</v>
       </c>
       <c r="D22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" t="s">
         <v>158</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>159</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>160</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
@@ -1767,22 +1740,22 @@
         <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F23" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="G23" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -1793,22 +1766,22 @@
         <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D24" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F24" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G24" t="s">
+        <v>190</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -1816,51 +1789,39 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="D25" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E25" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="F25" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G25" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>204</v>
-      </c>
-      <c r="E26" t="s">
-        <v>203</v>
-      </c>
-      <c r="F26" t="s">
-        <v>202</v>
-      </c>
-      <c r="G26" t="s">
-        <v>199</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
@@ -1868,13 +1829,13 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
@@ -1882,13 +1843,13 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -1896,13 +1857,13 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
@@ -1910,13 +1871,25 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>157</v>
+      </c>
+      <c r="E30" t="s">
+        <v>158</v>
+      </c>
+      <c r="F30" t="s">
+        <v>159</v>
+      </c>
+      <c r="G30" t="s">
+        <v>160</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -1924,25 +1897,13 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E31" t="s">
-        <v>165</v>
-      </c>
-      <c r="F31" t="s">
-        <v>166</v>
-      </c>
-      <c r="G31" t="s">
         <v>167</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
@@ -1950,53 +1911,39 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" t="s">
-        <v>183</v>
-      </c>
-      <c r="D34" t="s">
-        <v>176</v>
-      </c>
-      <c r="E34" t="s">
-        <v>184</v>
-      </c>
-      <c r="F34" t="s">
-        <v>185</v>
-      </c>
-      <c r="G34" t="s">
-        <v>186</v>
-      </c>
-      <c r="H34" t="s">
-        <v>187</v>
+        <v>169</v>
+      </c>
+      <c r="E33" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" t="s">
+        <v>178</v>
+      </c>
+      <c r="G33" t="s">
+        <v>179</v>
+      </c>
+      <c r="H33" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/data/reservation-data.xlsx
+++ b/data/reservation-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\2026_KDMHS\공업일반\webprojec\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1665BA2A-96DA-4557-A74C-2FB5EA194D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03C61CC-67D9-40F7-9099-E68F0FB80329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5856" yWindow="2076" windowWidth="17184" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
